--- a/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 570 684</t>
+            <t xml:space="preserve">3 570 640</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">459 942</t>
+            <t xml:space="preserve">460 002</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 508</t>
+            <t xml:space="preserve">143 538</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">779 561</t>
+            <t xml:space="preserve">779 518</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 135 718</t>
+            <t xml:space="preserve">1 135 648</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 343</t>
+            <t xml:space="preserve">545 341</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 970</t>
+            <t xml:space="preserve">309 948</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 293</t>
+            <t xml:space="preserve">84 302</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 349</t>
+            <t xml:space="preserve">112 343</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 577 146</t>
+            <t xml:space="preserve">1 577 345</t>
           </r>
         </is>
       </c>
@@ -497,7 +497,7 @@
       <c r="E12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">25.08</t>
+            <t xml:space="preserve">25.09</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 200 784</t>
+            <t xml:space="preserve">1 200 909</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">217 962</t>
+            <t xml:space="preserve">218 025</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">57 779</t>
+            <t xml:space="preserve">57 786</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 418</t>
+            <t xml:space="preserve">2 417</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 519</t>
+            <t xml:space="preserve">24 524</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 054 864</t>
+            <t xml:space="preserve">1 054 974</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 984</t>
+            <t xml:space="preserve">32 993</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 536</t>
+            <t xml:space="preserve">208 527</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">747 128</t>
+            <t xml:space="preserve">747 232</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 216</t>
+            <t xml:space="preserve">66 222</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 929</t>
+            <t xml:space="preserve">84 980</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 929</t>
+            <t xml:space="preserve">84 980</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46127.3202571529</v>
+        <v>46128.320272766054</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 570 640</t>
+            <t xml:space="preserve">3 570 481</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.79</t>
+            <t xml:space="preserve">56.78</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">460 002</t>
+            <t xml:space="preserve">460 159</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 538</t>
+            <t xml:space="preserve">143 583</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">779 518</t>
+            <t xml:space="preserve">779 397</t>
           </r>
         </is>
       </c>
@@ -341,7 +341,7 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12.40</t>
+            <t xml:space="preserve">12.39</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 135 648</t>
+            <t xml:space="preserve">1 135 440</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 341</t>
+            <t xml:space="preserve">545 360</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 948</t>
+            <t xml:space="preserve">309 888</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 302</t>
+            <t xml:space="preserve">84 330</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 343</t>
+            <t xml:space="preserve">112 324</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 577 345</t>
+            <t xml:space="preserve">1 577 764</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 200 909</t>
+            <t xml:space="preserve">1 201 167</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">218 025</t>
+            <t xml:space="preserve">218 155</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">57 786</t>
+            <t xml:space="preserve">57 806</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 682</t>
+            <t xml:space="preserve">32 675</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 021</t>
+            <t xml:space="preserve">40 023</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 417</t>
+            <t xml:space="preserve">2 416</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 524</t>
+            <t xml:space="preserve">24 541</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 054 974</t>
+            <t xml:space="preserve">1 055 279</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 993</t>
+            <t xml:space="preserve">33 022</t>
           </r>
         </is>
       </c>
@@ -757,7 +757,7 @@
       <c r="E22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">0.52</t>
+            <t xml:space="preserve">0.53</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 527</t>
+            <t xml:space="preserve">208 513</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">747 232</t>
+            <t xml:space="preserve">747 525</t>
           </r>
         </is>
       </c>
@@ -809,7 +809,7 @@
       <c r="E24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">11.88</t>
+            <t xml:space="preserve">11.89</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 222</t>
+            <t xml:space="preserve">66 219</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 980</t>
+            <t xml:space="preserve">85 073</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 980</t>
+            <t xml:space="preserve">85 073</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46128.320272766054</v>
+        <v>46131.32026893506</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 570 481</t>
+            <t xml:space="preserve">3 570 420</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.78</t>
+            <t xml:space="preserve">56.77</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">460 159</t>
+            <t xml:space="preserve">460 266</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 583</t>
+            <t xml:space="preserve">143 600</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">779 397</t>
+            <t xml:space="preserve">779 326</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 135 440</t>
+            <t xml:space="preserve">1 135 335</t>
           </r>
         </is>
       </c>
@@ -367,7 +367,7 @@
       <c r="E7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">18.06</t>
+            <t xml:space="preserve">18.05</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 360</t>
+            <t xml:space="preserve">545 363</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 888</t>
+            <t xml:space="preserve">309 859</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 330</t>
+            <t xml:space="preserve">84 358</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 324</t>
+            <t xml:space="preserve">112 313</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 577 764</t>
+            <t xml:space="preserve">1 577 948</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 201 167</t>
+            <t xml:space="preserve">1 201 271</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">218 155</t>
+            <t xml:space="preserve">218 214</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">57 806</t>
+            <t xml:space="preserve">57 817</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 675</t>
+            <t xml:space="preserve">32 674</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 023</t>
+            <t xml:space="preserve">40 029</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 416</t>
+            <t xml:space="preserve">2 417</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 541</t>
+            <t xml:space="preserve">24 545</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 055 279</t>
+            <t xml:space="preserve">1 055 434</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 022</t>
+            <t xml:space="preserve">33 041</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 513</t>
+            <t xml:space="preserve">208 516</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">747 525</t>
+            <t xml:space="preserve">747 647</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 219</t>
+            <t xml:space="preserve">66 230</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 073</t>
+            <t xml:space="preserve">85 141</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 073</t>
+            <t xml:space="preserve">85 141</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46131.32026893506</v>
+        <v>46133.320275301114</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 570 420</t>
+            <t xml:space="preserve">3 570 356</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">460 266</t>
+            <t xml:space="preserve">460 339</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 600</t>
+            <t xml:space="preserve">143 620</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">779 326</t>
+            <t xml:space="preserve">779 282</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 135 335</t>
+            <t xml:space="preserve">1 135 230</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 363</t>
+            <t xml:space="preserve">545 368</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 859</t>
+            <t xml:space="preserve">309 838</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 358</t>
+            <t xml:space="preserve">84 376</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 313</t>
+            <t xml:space="preserve">112 303</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 577 948</t>
+            <t xml:space="preserve">1 578 117</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 201 271</t>
+            <t xml:space="preserve">1 201 357</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">218 214</t>
+            <t xml:space="preserve">218 274</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">57 817</t>
+            <t xml:space="preserve">57 826</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 674</t>
+            <t xml:space="preserve">32 672</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 029</t>
+            <t xml:space="preserve">40 032</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 417</t>
+            <t xml:space="preserve">2 419</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 545</t>
+            <t xml:space="preserve">24 556</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 055 434</t>
+            <t xml:space="preserve">1 055 596</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 041</t>
+            <t xml:space="preserve">33 048</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 516</t>
+            <t xml:space="preserve">208 547</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">747 647</t>
+            <t xml:space="preserve">747 770</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 230</t>
+            <t xml:space="preserve">66 231</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 141</t>
+            <t xml:space="preserve">85 176</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 141</t>
+            <t xml:space="preserve">85 176</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46133.320275301114</v>
+        <v>46134.32026293967</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>
